--- a/server/upload/excel_template/list.xlsx
+++ b/server/upload/excel_template/list.xlsx
@@ -26,11 +26,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,###.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -52,6 +53,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Noto Sans CJK KR"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -102,7 +111,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -120,6 +129,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -132,6 +157,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -246,8 +331,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="6.23046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="6.23046875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.07"/>
@@ -258,7 +343,24 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="10.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="10.49"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -275,9 +377,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="4" width="9.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="8" width="9.51"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -296,9 +398,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="4" width="9.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="8" width="9.51"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -317,9 +419,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="4" width="9.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="8" width="9.51"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -338,9 +440,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.50390625" defaultRowHeight="12" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="4" width="9.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="8" width="9.51"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -359,7 +461,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.19140625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.19140625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
